--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_151_R16.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_151_R16.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.739100000000001</v>
+        <v>8.997999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.071</v>
+        <v>8.7668</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6681</v>
+        <v>0.2312</v>
       </c>
       <c r="G2" t="n">
         <v>5.3356</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5786</v>
+        <v>-0.3196</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.7177</v>
+        <v>-1.0218</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1391</v>
+        <v>0.7022</v>
       </c>
       <c r="V2" t="n">
         <v>2.8223</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2184</v>
+        <v>3.1393</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2238</v>
+        <v>3.2119</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0054</v>
+        <v>-0.0726</v>
       </c>
       <c r="G3" t="n">
         <v>1.0471</v>
@@ -688,13 +688,13 @@
         <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2926</v>
+        <v>-0.3716</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9313</v>
+        <v>-0.9432</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6388</v>
+        <v>0.5715</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7201</v>
+        <v>1.2393</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0972</v>
+        <v>1.818</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3771</v>
+        <v>-0.5787</v>
       </c>
       <c r="G4" t="n">
         <v>-1.965</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0677</v>
+        <v>-0.5485</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5579</v>
+        <v>-0.8371</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4903</v>
+        <v>0.2886</v>
       </c>
       <c r="V4" t="n">
         <v>3.7527</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5974</v>
+        <v>0.3332</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2413</v>
+        <v>2.1115</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6439</v>
+        <v>-1.7783</v>
       </c>
       <c r="G5" t="n">
         <v>0.458</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0518</v>
+        <v>-0.2124</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0351</v>
+        <v>-0.165</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.0474</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5182</v>
+        <v>0.0254</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8377</v>
+        <v>-0.4957</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3195</v>
+        <v>0.5212</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8846000000000001</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7934</v>
+        <v>-0.2497</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6721</v>
+        <v>-0.3301</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1212</v>
+        <v>0.0804</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2327</v>
+        <v>-1.5585</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1634</v>
+        <v>-0.7133</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0693</v>
+        <v>-0.8452</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0977</v>
+        <v>-2.6459</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8066</v>
+        <v>-1.1069</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.291</v>
+        <v>-1.539</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2176</v>
+        <v>-0.9445</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0336</v>
+        <v>-0.3053</v>
       </c>
       <c r="L7" t="n">
-        <v>0.184</v>
+        <v>-0.6391</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3153</v>
+        <v>-1.7015</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8401999999999999</v>
+        <v>-0.8016</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4751</v>
+        <v>-0.8999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.651</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.637</v>
+        <v>-0.841</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0141</v>
+        <v>0.2326</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4986</v>
+        <v>-1.7717</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2165</v>
+        <v>-0.6352</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2821</v>
+        <v>-1.1365</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.6459</v>
+        <v>-1.0977</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1069</v>
+        <v>-0.8066</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.539</v>
+        <v>-0.291</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9445</v>
+        <v>0.2176</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3053</v>
+        <v>0.0336</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6391</v>
+        <v>0.184</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7015</v>
+        <v>-1.3153</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8016</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8999</v>
+        <v>-0.4751</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5485</v>
+        <v>0.112</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3443</v>
+        <v>0.1652</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2043</v>
+        <v>-0.0532</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.7876</v>
+        <v>-4.6024</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.554</v>
+        <v>-1.4361</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.2336</v>
+        <v>-3.1664</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8299</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4216</v>
+        <v>-1.2364</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8988</v>
+        <v>-0.8316</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1921</v>
+        <v>-4.6366</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7992</v>
+        <v>-2.4454</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3929</v>
+        <v>-2.1913</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0921</v>
+        <v>-0.5366</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0455</v>
+        <v>-0.6917</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0466</v>
+        <v>0.1551</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04579999999999806</v>
+        <v>1.165999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>9.0625</v>
+        <v>10.1825</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.0167</v>
+        <v>-9.0166</v>
       </c>
       <c r="G11" t="n">
         <v>-5.682399999999999</v>
@@ -1312,13 +1312,13 @@
         <v>12.7576</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.0917</v>
+        <v>-3.9712</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.1897</v>
+        <v>-5.069500000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0984</v>
+        <v>1.0982</v>
       </c>
       <c r="V11" t="n">
         <v>6.180699999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.6333</v>
+        <v>3.8247</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0419</v>
+        <v>4.3342</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4086</v>
+        <v>-0.5094</v>
       </c>
       <c r="G12" t="n">
         <v>1.365</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7295</v>
+        <v>0.921</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5508999999999999</v>
+        <v>-0.1568</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1787</v>
+        <v>1.0778</v>
       </c>
       <c r="V12" t="n">
         <v>2.0026</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5191</v>
+        <v>2.2832</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3465</v>
+        <v>1.1106</v>
       </c>
       <c r="F13" t="n">
         <v>1.1726</v>
@@ -1468,10 +1468,10 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0104</v>
+        <v>0.7745</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7943</v>
+        <v>0.5583</v>
       </c>
       <c r="U13" t="n">
         <v>0.2161</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7773</v>
+        <v>2.2827</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3228</v>
+        <v>3.7946</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5455</v>
+        <v>-1.5119</v>
       </c>
       <c r="G14" t="n">
         <v>1.8192</v>
@@ -1546,13 +1546,13 @@
         <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0303</v>
+        <v>0.5357</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.4007</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9028</v>
+        <v>0.9364</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5361</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6744</v>
+        <v>1.7759</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6805</v>
+        <v>2.9164</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0061</v>
+        <v>-1.1405</v>
       </c>
       <c r="G15" t="n">
         <v>1.3702</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3585</v>
+        <v>0.4599</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6493</v>
+        <v>0.5149</v>
       </c>
       <c r="V15" t="n">
         <v>-1.214</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0976</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5946</v>
+        <v>1.2408</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4971</v>
+        <v>-0.329</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1979</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3677</v>
+        <v>0.1819</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5702</v>
+        <v>0.2164</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6237</v>
+        <v>-0.3707</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5154</v>
+        <v>-0.1615</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1083</v>
+        <v>-0.2091</v>
       </c>
       <c r="G17" t="n">
         <v>0.3713</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3967</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1256</v>
+        <v>0.2282</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5223</v>
+        <v>0.4215</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0118</v>
+        <v>-0.7252</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5222</v>
+        <v>-1.1683</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5104</v>
+        <v>0.4432</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1088</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0448</v>
+        <v>0.2418</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0965</v>
+        <v>-0.7426</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0517</v>
+        <v>0.9845</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3943</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>I. LUNDBERG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2794</v>
+        <v>-2.3884</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2094</v>
+        <v>-1.125</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4887</v>
+        <v>-1.2635</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2052</v>
+        <v>2.4536</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4347</v>
+        <v>0.8812</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.6399</v>
+        <v>1.5724</v>
       </c>
       <c r="J19" t="n">
-        <v>0.386</v>
+        <v>3.6369</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0251</v>
+        <v>2.2687</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6391</v>
+        <v>1.3682</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5912</v>
+        <v>-1.1833</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5904</v>
+        <v>-1.3875</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0008</v>
+        <v>0.2042</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-3.7112</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9801</v>
+        <v>0.8718</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1766</v>
+        <v>0.2715</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1567</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.7501</v>
+        <v>-2.0026</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7501</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. LUNDBERG</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0955</v>
+        <v>-3.0029</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5968</v>
+        <v>-0.1445</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4987</v>
+        <v>-2.8584</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4536</v>
+        <v>-2.2052</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8812</v>
+        <v>0.4347</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5724</v>
+        <v>-2.6399</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6369</v>
+        <v>0.386</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2687</v>
+        <v>1.0251</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3682</v>
+        <v>-0.6391</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1833</v>
+        <v>-2.5912</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3875</v>
+        <v>-0.5904</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2042</v>
+        <v>-2.0008</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.7112</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1647</v>
+        <v>0.2566</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2003</v>
+        <v>-0.5305</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3651</v>
+        <v>0.787</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.0026</v>
+        <v>-1.7501</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.737</v>
+        <v>-4.6368</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5446</v>
+        <v>-1.7805</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1924</v>
+        <v>-2.8563</v>
       </c>
       <c r="G21" t="n">
         <v>0.2342</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0984</v>
+        <v>0.1986</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2513</v>
+        <v>-0.4872</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3497</v>
+        <v>0.6858</v>
       </c>
       <c r="V21" t="n">
         <v>-2.2862</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0456999999999983</v>
+        <v>-0.04570000000000096</v>
       </c>
       <c r="E22" t="n">
-        <v>9.0167</v>
+        <v>9.016799999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>-9.0624</v>
+        <v>-9.0623</v>
       </c>
       <c r="G22" t="n">
         <v>5.6825</v>
@@ -2140,7 +2140,7 @@
         <v>-0.6244000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>6.307000000000001</v>
+        <v>6.307</v>
       </c>
       <c r="J22" t="n">
         <v>19.7665</v>
@@ -2155,7 +2155,7 @@
         <v>-14.0839</v>
       </c>
       <c r="N22" t="n">
-        <v>-9.835799999999999</v>
+        <v>-9.835800000000001</v>
       </c>
       <c r="O22" t="n">
         <v>-4.2483</v>
@@ -2173,10 +2173,10 @@
         <v>5.0915</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0982</v>
+        <v>-1.0983</v>
       </c>
       <c r="U22" t="n">
-        <v>6.189900000000001</v>
+        <v>6.1898</v>
       </c>
       <c r="V22" t="n">
         <v>-6.1807</v>
